--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260925.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>見える化の第10期3年計3,101,295千円に対し、こちらの算定は2,876,614千円。差は1.9％</t>
+          <t>見える化の第10期3年計3,101,295千円に対し、こちらの算定は2,869,936千円。差は1.9％</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1001,16 +1001,16 @@
       <c r="D3" s="7" t="inlineStr"/>
       <c r="E3" s="7" t="inlineStr"/>
       <c r="F3" s="7" t="n">
-        <v>961668.5315123043</v>
+        <v>960695.3069189452</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>958871.3571914423</v>
+        <v>956645.1905726381</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>956074.1828705806</v>
+        <v>952595.0742263311</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>2876614.071574328</v>
+        <v>2869935.571717914</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
       <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="7" t="n">
-        <v>73523.46848769567</v>
+        <v>74496.69308105484</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>81311.64280855772</v>
+        <v>83537.80942736194</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>69845.81712941942</v>
+        <v>73324.92577366892</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>224680.9284256725</v>
+        <v>231359.4282820858</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -1219,16 +1219,16 @@
       <c r="D12" s="7" t="inlineStr"/>
       <c r="E12" s="7" t="inlineStr"/>
       <c r="F12" s="7" t="n">
-        <v>354268.0379936694</v>
+        <v>352690.1633816847</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>353237.5899483126</v>
+        <v>349978.7959198076</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>352207.1419029558</v>
+        <v>347267.4284579305</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>1059712.769844938</v>
+        <v>1049936.387759423</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1251,16 +1251,16 @@
       <c r="D13" s="7" t="inlineStr"/>
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="n">
-        <v>318766.8214768927</v>
+        <v>318447.9780713011</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>317839.6346779488</v>
+        <v>317109.2291868711</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>316912.447879005</v>
+        <v>315770.4803024413</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>953518.9040338467</v>
+        <v>951327.6875606135</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1283,16 +1283,16 @@
       <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="7" t="n">
-        <v>288633.6720417421</v>
+        <v>289557.1654659594</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>287794.1325651808</v>
+        <v>289557.1654659594</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>286954.5930886197</v>
+        <v>289557.1654659594</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>863382.3976955425</v>
+        <v>868671.4963978783</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1573,22 +1573,22 @@
         <v>695916</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>195989.271515613</v>
+        <v>196616.3459736327</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>195419.2038265042</v>
+        <v>196616.3459736327</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>194849.1361373954</v>
+        <v>196616.3459736327</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>586257.6114795126</v>
+        <v>589849.0379208982</v>
       </c>
       <c r="L2" s="9" t="n">
-        <v>109658.3885204874</v>
+        <v>106066.9620791018</v>
       </c>
       <c r="M2" s="10" t="n">
-        <v>0.1870481276034051</v>
+        <v>0.1798205223034135</v>
       </c>
       <c r="N2" s="11" t="n">
         <v>1.039988078859075</v>
@@ -1628,22 +1628,22 @@
         <v>128075</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>14901.77983645077</v>
+        <v>14834.86575542286</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>14858.43550882875</v>
+        <v>14720.27291401073</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>14815.09118120673</v>
+        <v>14605.6800725986</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>44575.30652648625</v>
+        <v>44160.8187420322</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>83499.69347351376</v>
+        <v>83914.18125796781</v>
       </c>
       <c r="M3" s="10" t="n">
-        <v>1.873227577782309</v>
+        <v>1.90019532355496</v>
       </c>
       <c r="N3" s="11" t="n">
         <v>2.652980267830544</v>
@@ -1683,22 +1683,22 @@
         <v>332839</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>128567.6907506041</v>
+        <v>128168.8776307649</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>128193.7300445232</v>
+        <v>127358.7077342366</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>127819.7693384424</v>
+        <v>126548.5378377084</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>384581.1901335697</v>
+        <v>382076.1232027099</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>-51742.1901335697</v>
+        <v>-49237.12320270989</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>-0.1345416558610134</v>
+        <v>-0.1288673125920177</v>
       </c>
       <c r="N4" s="11" t="n">
         <v>0.8590987863434963</v>
@@ -1738,22 +1738,22 @@
         <v>177624</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>47434.38751653285</v>
+        <v>47221.3909158163</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>47296.41663952141</v>
+        <v>46856.62635038717</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>47158.44576250997</v>
+        <v>46491.86178495803</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>141889.2499185642</v>
+        <v>140569.8790511615</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>35734.75008143578</v>
+        <v>37054.12094883848</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>0.2518495946799728</v>
+        <v>0.2635992945213557</v>
       </c>
       <c r="N5" s="11" t="n">
         <v>1.219083990352523</v>
@@ -1793,22 +1793,22 @@
         <v>111049</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>26208.83074636502</v>
+        <v>26091.14414493508</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>26132.59796350764</v>
+        <v>25889.60148236204</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>26056.36518065027</v>
+        <v>25688.058819789</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>78397.79389052292</v>
+        <v>77668.80444708612</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>32651.20610947708</v>
+        <v>33380.19555291388</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>0.4164811851092676</v>
+        <v>0.4297760959569681</v>
       </c>
       <c r="N6" s="11" t="n">
         <v>1.648007795878797</v>
@@ -1848,22 +1848,22 @@
         <v>155121</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>46001.05714140301</v>
+        <v>45794.49668361124</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>45867.25534634366</v>
+        <v>45440.75425125421</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>45733.45355128431</v>
+        <v>45087.01181889718</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>137601.766039031</v>
+        <v>136322.2627537626</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>17519.23396096902</v>
+        <v>18798.73724623738</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>0.1273183801725311</v>
+        <v>0.1378992459961828</v>
       </c>
       <c r="N7" s="11" t="n">
         <v>1.081346804772154</v>
@@ -1899,22 +1899,22 @@
         <v>346548</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>120884.6126949831</v>
+        <v>121271.3871974976</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>120532.999510879</v>
+        <v>121271.3871974976</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>120181.3863267749</v>
+        <v>121271.3871974976</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>361598.998532637</v>
+        <v>363814.1615924927</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>-15050.99853263702</v>
+        <v>-17266.16159249272</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>-0.04162345192800243</v>
+        <v>-0.04745873969532965</v>
       </c>
       <c r="N8" s="11" t="n">
         <v>0.9368840744492987</v>
@@ -1950,22 +1950,22 @@
         <v>99954</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>28460.72320953207</v>
+        <v>28332.9248418299</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>28377.94041951016</v>
+        <v>28114.06540510363</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>28295.15762948825</v>
+        <v>27895.20596837737</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>85133.82125853047</v>
+        <v>84342.19621531091</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>14820.17874146953</v>
+        <v>15611.80378468909</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>0.1740809765423814</v>
+        <v>0.185100750101822</v>
       </c>
       <c r="N9" s="11" t="n">
         <v>1.149042609214904</v>
@@ -2001,22 +2001,22 @@
         <v>99994</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>29950.75519359016</v>
+        <v>29816.26607337322</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>29863.63839547035</v>
+        <v>29585.94847522448</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>29776.52159735055</v>
+        <v>29355.63087707574</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>89590.91518641106</v>
+        <v>88757.84542567344</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>10403.08481358894</v>
+        <v>11236.15457432656</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>0.1161176308104825</v>
+        <v>0.1265933678362643</v>
       </c>
       <c r="N10" s="11" t="n">
         <v>1.107866739895231</v>
@@ -2036,41 +2036,41 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>特定施設入居者生活介護</t>
+          <t>通所介護</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>12411</v>
+        <v>149092</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>12411</v>
+        <v>148412</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>12411</v>
+        <v>144891</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>37233</v>
+        <v>442395</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>9298.574009786516</v>
+        <v>145239.7779897634</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>9271.527546698131</v>
+        <v>144117.8643088236</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>9244.481083609748</v>
+        <v>142995.9506278838</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>27814.58264009439</v>
+        <v>432353.5929264707</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>9418.417359905608</v>
+        <v>10041.40707352932</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>0.3386143693678536</v>
+        <v>0.0232249881527804</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>1.175016544112426</v>
+        <v>0.9973714126232121</v>
       </c>
       <c r="O11" s="3" t="inlineStr"/>
     </row>
@@ -2082,46 +2082,46 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>施設</t>
+          <t>居宅</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>介護老人保健施設</t>
+          <t>特定施設入居者生活介護</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>85683</v>
+        <v>12411</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>85683</v>
+        <v>12411</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>85683</v>
+        <v>12411</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>257049</v>
+        <v>37233</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>88521.17318640625</v>
+        <v>9269.730112153689</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>88263.69449767323</v>
+        <v>9211.135105123642</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>88006.21580894024</v>
+        <v>9152.540098093594</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>264791.0834930197</v>
+        <v>27633.40531537092</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>-7742.083493019687</v>
+        <v>9599.594684629075</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>-0.02923845996205454</v>
+        <v>0.347390941328876</v>
       </c>
       <c r="N12" s="11" t="n">
-        <v>0.960264884408101</v>
+        <v>1.175016544112426</v>
       </c>
       <c r="O12" s="3" t="inlineStr"/>
     </row>
@@ -2133,46 +2133,46 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>居宅</t>
+          <t>施設</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>通所介護</t>
+          <t>介護老人保健施設</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>149092</v>
+        <v>85683</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>148412</v>
+        <v>85683</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>144891</v>
+        <v>85683</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>442395</v>
+        <v>257049</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>145894.8959013851</v>
+        <v>88804.39974401254</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>145470.5361110961</v>
+        <v>88804.39974401254</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>145046.176320807</v>
+        <v>88804.39974401254</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>436411.6083332882</v>
+        <v>266413.1992320376</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>5983.391666711774</v>
+        <v>-9364.199232037645</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>0.01371043196940414</v>
+        <v>-0.03514915649461392</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>0.9973714126232121</v>
+        <v>0.960264884408101</v>
       </c>
       <c r="O13" s="3" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>29508</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>11708.48184507844</v>
+        <v>11655.90676267259</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>11674.42576059596</v>
+        <v>11565.86998733599</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>11640.36967611347</v>
+        <v>11475.8332119994</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>35023.27728178787</v>
+        <v>34697.60996200798</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>-5515.277281787872</v>
+        <v>-5189.609962007977</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>-0.1574746200195212</v>
+        <v>-0.1495667847926794</v>
       </c>
       <c r="N14" s="11" t="n">
         <v>0.794395049324225</v>
@@ -2256,19 +2256,19 @@
         <v>0</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1734.575551770097</v>
+        <v>1726.786715114743</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1729.530247663727</v>
+        <v>1713.448043942381</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1724.484943557357</v>
+        <v>1700.109372770019</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>5188.590742991181</v>
+        <v>5140.344131827143</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>-5188.590742991181</v>
+        <v>-5140.344131827143</v>
       </c>
       <c r="M15" s="10" t="n">
         <v>-1</v>
@@ -2311,22 +2311,22 @@
         <v>52812</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>19313.69887587554</v>
+        <v>19226.97377151131</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>19257.52174127439</v>
+        <v>19078.45381908582</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>19201.34460667324</v>
+        <v>18929.93386666033</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>57772.56522382317</v>
+        <v>57235.36145725746</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>-4960.565223823171</v>
+        <v>-4423.361457257459</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>-0.08586368295409574</v>
+        <v>-0.07728371665060174</v>
       </c>
       <c r="N16" s="11" t="n">
         <v>0.9477114438352204</v>
@@ -2362,22 +2362,22 @@
         <v>2367</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>2226.956766997357</v>
+        <v>2216.956970517475</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>2220.479289490092</v>
+        <v>2199.831948779603</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>2214.001811982829</v>
+        <v>2182.706927041732</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>6661.437868470279</v>
+        <v>6599.49584633881</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>-4294.437868470279</v>
+        <v>-4232.49584633881</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>-0.6446713086969684</v>
+        <v>-0.6413362391442164</v>
       </c>
       <c r="N17" s="11" t="n">
         <v>0.283799406432614</v>
@@ -2391,7 +2391,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>介護</t>
+          <t>予防</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2401,52 +2401,48 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>特定福祉用具販売</t>
+          <t>介護予防通所リハビリテーション</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>321</v>
+        <v>12366</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>321</v>
+        <v>12366</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>321</v>
+        <v>12366</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>963</v>
+        <v>37098</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1648.044485942075</v>
+        <v>11133.34460647689</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>1643.250871963186</v>
+        <v>11047.34439495423</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1638.457257984297</v>
+        <v>10961.34418343157</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>4929.752615889559</v>
+        <v>33142.0331848627</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>-3966.752615889559</v>
+        <v>3955.966815137304</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>-0.8046555121455664</v>
+        <v>0.1193640351837</v>
       </c>
       <c r="N18" s="11" t="n">
-        <v>0.2140543397455318</v>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>見える化の令和8年度基準値が令和7年度実績と大きく違う。04参照</t>
-        </is>
-      </c>
+        <v>1.097472208875912</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>予防</t>
+          <t>介護</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2456,43 +2452,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>介護予防通所リハビリテーション</t>
+          <t>特定福祉用具販売</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>12366</v>
+        <v>321</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>12366</v>
+        <v>321</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>12366</v>
+        <v>321</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>37098</v>
+        <v>963</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>11183.56262229123</v>
+        <v>1640.644203326157</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>11151.03335346548</v>
+        <v>1627.970945333461</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>11118.50408463974</v>
+        <v>1615.297687340765</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>33453.10006039645</v>
+        <v>4883.912836000384</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>3644.899939603551</v>
+        <v>-3920.912836000384</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>0.1089555208044404</v>
+        <v>-0.8028220338206044</v>
       </c>
       <c r="N19" s="11" t="n">
-        <v>1.097472208875912</v>
-      </c>
-      <c r="O19" s="3" t="inlineStr"/>
+        <v>0.2140543397455318</v>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>見える化の令和8年度基準値が令和7年度実績と大きく違う。04参照</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2523,22 +2523,22 @@
         <v>5475</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>3033.283018088922</v>
+        <v>3019.66254134852</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>3024.460205354516</v>
+        <v>2996.33697060027</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>3015.637392620109</v>
+        <v>2973.011399852021</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>9073.380616063547</v>
+        <v>8989.010911800811</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>-3598.380616063547</v>
+        <v>-3514.010911800811</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>-0.3965865390561221</v>
+        <v>-0.3909229776534816</v>
       </c>
       <c r="N20" s="11" t="n">
         <v>0.7313467709948437</v>
@@ -2574,22 +2574,22 @@
         <v>20523</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>5740.852055887209</v>
+        <v>5715.073669422444</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>5724.153824194692</v>
+        <v>5670.927228095911</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>5707.455592502176</v>
+        <v>5626.780786769378</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>17172.46147258408</v>
+        <v>17012.78168428773</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>3350.538527415923</v>
+        <v>3510.218315712267</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>0.195111139586196</v>
+        <v>0.2063282995604507</v>
       </c>
       <c r="N21" s="11" t="n">
         <v>1.172920901278152</v>
@@ -2625,22 +2625,22 @@
         <v>4116</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>463.1229362660712</v>
+        <v>461.0433561069692</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>461.775865479957</v>
+        <v>457.4819980831414</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>460.4287946938428</v>
+        <v>453.9206400593138</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>1385.327596439871</v>
+        <v>1372.445994249425</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>2730.672403560129</v>
+        <v>2743.554005750575</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>1.971138386745226</v>
+        <v>1.999025110821206</v>
       </c>
       <c r="N22" s="11" t="n">
         <v>1.511125794994631</v>
@@ -2680,19 +2680,19 @@
         <v>0</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>838.8269455198565</v>
+        <v>835.0603260410468</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>836.3870765683735</v>
+        <v>828.6098507156058</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>833.9472076168905</v>
+        <v>822.159375390165</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>2509.161229705121</v>
+        <v>2485.829552146818</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>-2509.161229705121</v>
+        <v>-2485.829552146818</v>
       </c>
       <c r="M23" s="10" t="n">
         <v>-1</v>
@@ -2735,22 +2735,22 @@
         <v>13663</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>3966.653785275391</v>
+        <v>3948.842155006346</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>3955.116107016882</v>
+        <v>3918.339078652941</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>3943.578428758373</v>
+        <v>3887.836002299536</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>11865.34832105065</v>
+        <v>11755.01723595882</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>1797.651678949353</v>
+        <v>1907.982764041177</v>
       </c>
       <c r="M24" s="10" t="n">
-        <v>0.1515043326423118</v>
+        <v>0.1623122047158401</v>
       </c>
       <c r="N24" s="11" t="n">
         <v>1.131671197508029</v>
@@ -2786,22 +2786,22 @@
         <v>7761</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>2118.064611084613</v>
+        <v>2108.553777575868</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>2111.903864688206</v>
+        <v>2092.266123031075</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>2105.743118291799</v>
+        <v>2075.978468486283</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>6335.711594064618</v>
+        <v>6276.798369093225</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>1425.288405935382</v>
+        <v>1484.201630906775</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>0.2249610615594642</v>
+        <v>0.2364583890753829</v>
       </c>
       <c r="N25" s="11" t="n">
         <v>1.059904507614313</v>
@@ -2837,22 +2837,22 @@
         <v>8475</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>3198.762930040986</v>
+        <v>3188.840463390866</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>3189.458791210151</v>
+        <v>3168.683444026828</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>3180.154652379316</v>
+        <v>3148.526424662789</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>9568.376373630454</v>
+        <v>9506.050332080482</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>-1093.376373630454</v>
+        <v>-1031.050332080482</v>
       </c>
       <c r="M26" s="10" t="n">
-        <v>-0.114269791544122</v>
+        <v>-0.1084625366016579</v>
       </c>
       <c r="N26" s="11" t="n">
         <v>0.8470586965541886</v>
@@ -2888,19 +2888,19 @@
         <v>0</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>280.287634354361</v>
+        <v>279.029047146514</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>279.4723707291301</v>
+        <v>276.8736699509132</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>278.6571071038993</v>
+        <v>274.7182927553123</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>838.4171121873904</v>
+        <v>830.6210098527395</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>-838.4171121873904</v>
+        <v>-830.6210098527395</v>
       </c>
       <c r="M27" s="10" t="n">
         <v>-1</v>
@@ -2943,22 +2943,22 @@
         <v>11610</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>4123.227339722805</v>
+        <v>4136.419748314122</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>4111.234241003425</v>
+        <v>4136.419748314122</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>4099.241142284045</v>
+        <v>4136.419748314122</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>12333.70272301028</v>
+        <v>12409.25924494237</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>-723.7027230102758</v>
+        <v>-799.2592449423682</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>-0.05867684176140431</v>
+        <v>-0.06440829618964738</v>
       </c>
       <c r="N28" s="11" t="n">
         <v>0.983647959883971</v>
@@ -2994,22 +2994,22 @@
         <v>2112</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>829.004981168934</v>
+        <v>825.2824656646592</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>826.5936810491872</v>
+        <v>818.907520028663</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>824.1823809294406</v>
+        <v>812.5325743926669</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>2479.781043147562</v>
+        <v>2456.722560085989</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>-367.7810431475618</v>
+        <v>-344.7225600859892</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>-0.1483119020382303</v>
+        <v>-0.1403180667148363</v>
       </c>
       <c r="N29" s="11" t="n">
         <v>0.8595070801043693</v>
@@ -3045,22 +3045,22 @@
         <v>20625</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>6972.88573965323</v>
+        <v>6941.575101158881</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>6952.603931219102</v>
+        <v>6887.954473386991</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>6932.322122784974</v>
+        <v>6834.3338456151</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>20857.81179365731</v>
+        <v>20663.86342016097</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>-232.8117936573071</v>
+        <v>-38.86342016097115</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>-0.01116185129871117</v>
+        <v>-0.001880743178115152</v>
       </c>
       <c r="N30" s="11" t="n">
         <v>1.01416693712566</v>
@@ -3206,7 +3206,7 @@
         <v>920.6</v>
       </c>
       <c r="H2" s="13" t="n">
-        <v>757.9030547427442</v>
+        <v>754.4998111723148</v>
       </c>
       <c r="I2" s="13" t="n">
         <v>51.16666666666666</v>
@@ -3218,7 +3218,7 @@
         <v>60</v>
       </c>
       <c r="L2" s="13" t="n">
-        <v>48.95355308353092</v>
+        <v>48.73373491056189</v>
       </c>
       <c r="M2" s="3" t="inlineStr"/>
     </row>
@@ -3251,7 +3251,7 @@
         <v>12.6</v>
       </c>
       <c r="H3" s="13" t="n">
-        <v>16.34442733244925</v>
+        <v>16.27103527144167</v>
       </c>
       <c r="I3" s="13" t="n">
         <v>4.833333333333333</v>
@@ -3263,7 +3263,7 @@
         <v>4</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>4.624277001375885</v>
+        <v>4.603512418261547</v>
       </c>
       <c r="M3" s="3" t="inlineStr"/>
     </row>
@@ -3296,7 +3296,7 @@
         <v>256.2</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>261.032463836287</v>
+        <v>259.860338920488</v>
       </c>
       <c r="I4" s="13" t="n">
         <v>41.83333333333334</v>
@@ -3308,7 +3308,7 @@
         <v>46</v>
       </c>
       <c r="L4" s="13" t="n">
-        <v>40.02391473604646</v>
+        <v>39.84419368909132</v>
       </c>
       <c r="M4" s="3" t="inlineStr"/>
     </row>
@@ -3343,7 +3343,7 @@
         <v>4</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>8.690451606033992</v>
+        <v>8.651428510181184</v>
       </c>
       <c r="M5" s="3" t="inlineStr"/>
     </row>
@@ -3376,7 +3376,7 @@
         <v>1482.5</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>1465.018791384171</v>
+        <v>1458.440356647516</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>167.5</v>
@@ -3388,7 +3388,7 @@
         <v>180</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>160.2551167718195</v>
+        <v>159.5355165638915</v>
       </c>
       <c r="M6" s="3" t="inlineStr"/>
     </row>
@@ -3421,7 +3421,7 @@
         <v>365.7</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>177.6360199838875</v>
+        <v>176.8383735842539</v>
       </c>
       <c r="I7" s="13" t="n">
         <v>26.5</v>
@@ -3433,7 +3433,7 @@
         <v>30</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>25.35379459375054</v>
+        <v>25.23994739667538</v>
       </c>
       <c r="M7" s="3" t="inlineStr"/>
     </row>
@@ -3466,7 +3466,7 @@
         <v>372.7</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>226.3503863259679</v>
+        <v>225.3339957835264</v>
       </c>
       <c r="I8" s="13" t="n">
         <v>25.58333333333333</v>
@@ -3478,7 +3478,7 @@
         <v>37</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>24.47677654176546</v>
+        <v>24.36686745528095</v>
       </c>
       <c r="M8" s="3" t="inlineStr"/>
     </row>
@@ -3511,7 +3511,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>20.09168628184005</v>
+        <v>20.00146774830879</v>
       </c>
       <c r="I9" s="13" t="n">
         <v>3.25</v>
@@ -3523,7 +3523,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>3.109427638856199</v>
+        <v>3.095465246762075</v>
       </c>
       <c r="M9" s="3" t="inlineStr"/>
     </row>
@@ -3558,7 +3558,7 @@
         <v>204</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>184.4927065721345</v>
+        <v>183.6642713078831</v>
       </c>
       <c r="M10" s="3" t="inlineStr"/>
     </row>
@@ -3593,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>3.826987863207629</v>
+        <v>3.809803380630246</v>
       </c>
       <c r="M11" s="3" t="inlineStr"/>
     </row>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>3.029698725039373</v>
+        <v>3.016094342998944</v>
       </c>
       <c r="M12" s="3" t="inlineStr"/>
     </row>
@@ -3663,7 +3663,7 @@
         <v>5</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>3.826987863207629</v>
+        <v>3.815116661660785</v>
       </c>
       <c r="M13" s="3" t="inlineStr"/>
     </row>
@@ -3696,7 +3696,7 @@
         <v>75.3</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>91.13014849263168</v>
+        <v>90.72094300125772</v>
       </c>
       <c r="I14" s="13" t="n">
         <v>9</v>
@@ -3708,7 +3708,7 @@
         <v>8</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>8.610722692217166</v>
+        <v>8.572057606418053</v>
       </c>
       <c r="M14" s="3" t="inlineStr"/>
     </row>
@@ -3743,7 +3743,7 @@
         <v>28</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>21.28761998909244</v>
+        <v>21.19203130475574</v>
       </c>
       <c r="M15" s="3" t="inlineStr"/>
     </row>
@@ -3778,7 +3778,7 @@
         <v>38</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>42.6549688920017</v>
+        <v>42.52265445809417</v>
       </c>
       <c r="M16" s="3" t="inlineStr"/>
     </row>
@@ -3813,7 +3813,7 @@
         <v>40</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>39.06716777024455</v>
+        <v>39.19216452576308</v>
       </c>
       <c r="M17" s="3" t="inlineStr"/>
     </row>
@@ -3848,7 +3848,7 @@
         <v>71</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>68.00876348575224</v>
+        <v>68.22635987852225</v>
       </c>
       <c r="M18" s="3" t="inlineStr"/>
     </row>
@@ -3883,7 +3883,7 @@
         <v>27</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>26.62945721481975</v>
+        <v>26.71465908490789</v>
       </c>
       <c r="M19" s="3" t="inlineStr"/>
     </row>
@@ -3918,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0.9567469658019073</v>
+        <v>0.9598081108350141</v>
       </c>
       <c r="M20" s="3" t="inlineStr"/>
     </row>
@@ -3953,7 +3953,7 @@
         <v>268</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>243.9704762794864</v>
+        <v>242.8749655151782</v>
       </c>
       <c r="M21" s="3" t="inlineStr"/>
     </row>
@@ -3986,7 +3986,7 @@
         <v>35</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>30.85508964711151</v>
+        <v>30.71653975633135</v>
       </c>
       <c r="I22" s="13" t="n">
         <v>7.583333333333333</v>
@@ -3998,7 +3998,7 @@
         <v>9</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>7.25533115733113</v>
+        <v>7.22275224244484</v>
       </c>
       <c r="M22" s="3" t="inlineStr"/>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="K23" s="13" t="n"/>
       <c r="L23" s="13" t="n">
-        <v>1.99322284542064</v>
+        <v>1.984272594078253</v>
       </c>
       <c r="M23" s="3" t="inlineStr"/>
     </row>
@@ -4064,7 +4064,7 @@
         <v>29</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>25.8321680766515</v>
+        <v>25.71617281925416</v>
       </c>
       <c r="M24" s="3" t="inlineStr"/>
     </row>
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>3.029698725039374</v>
+        <v>3.016094342998945</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>0.75</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0.7175602243514305</v>
+        <v>0.714338133868171</v>
       </c>
       <c r="M25" s="3" t="inlineStr"/>
     </row>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.398644569084128</v>
+        <v>0.3968545188156506</v>
       </c>
       <c r="I26" s="13" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0.07972891381682561</v>
+        <v>0.07937090376313011</v>
       </c>
       <c r="M26" s="3" t="inlineStr"/>
     </row>
@@ -4187,7 +4187,7 @@
         <v>64</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>51.90352289475347</v>
+        <v>51.67045834979771</v>
       </c>
       <c r="M27" s="3" t="inlineStr"/>
     </row>
@@ -4222,7 +4222,7 @@
         <v>3</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>2.391867414504768</v>
+        <v>2.381127112893903</v>
       </c>
       <c r="M28" s="3" t="inlineStr"/>
     </row>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>1.754036103970163</v>
+        <v>1.746159882788862</v>
       </c>
       <c r="M29" s="3" t="inlineStr"/>
     </row>
@@ -4292,7 +4292,7 @@
         <v>7</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>6.776957674430177</v>
+        <v>6.74652681986606</v>
       </c>
       <c r="M30" s="3" t="inlineStr"/>
     </row>
@@ -4327,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>1.116204793435559</v>
+        <v>1.112742359651062</v>
       </c>
       <c r="M31" s="3" t="inlineStr"/>
     </row>
@@ -4362,7 +4362,7 @@
         <v>85</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>71.51683569369257</v>
+        <v>71.19570067552772</v>
       </c>
       <c r="M32" s="3" t="inlineStr"/>
     </row>
@@ -5933,10 +5933,10 @@
         <v>3101295</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>2876614.071574328</v>
+        <v>2869935.571717914</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>224680.9284256725</v>
+        <v>231359.4282820858</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -5954,10 +5954,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>143634.4049844727</v>
+        <v>143300.9357288837</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-143634.4049844727</v>
+        <v>-143300.9357288837</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -5975,10 +5975,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>70781.49631659115</v>
+        <v>70617.16623920668</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-70781.49631659115</v>
+        <v>-70617.16623920668</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -5996,10 +5996,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7642.733186603193</v>
+        <v>7624.989411727824</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-7642.733186603193</v>
+        <v>-7624.989411727824</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>2487.785755966721</v>
+        <v>2469.503914049903</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-2487.785755966721</v>
+        <v>-2469.503914049903</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
         <v>3101295</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>3101160.491817961</v>
+        <v>3093948.167011783</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>134.5081820390187</v>
+        <v>7346.832988217473</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr"/>
       <c r="C20" s="7" t="n">
-        <v>5926</v>
+        <v>5912</v>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr"/>
       <c r="D21" s="7" t="n">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>第10期3年計 143,634千円</t>
+          <t>第10期3年計 143,301千円</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>第10期3年計 70,781千円</t>
+          <t>第10期3年計 70,617千円</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7,643千円</t>
+          <t>7,625千円</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260925.xlsx
@@ -6164,10 +6164,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0.9524214347952366</v>
+        <v>0.9959047342433923</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.9524214347952366</v>
+        <v>-0.9959047342433923</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -6185,14 +6185,14 @@
         <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6.1481</v>
+        <v>5.533219116080939</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>-6.1481</v>
+        <v>-5.533219116080939</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>**見える化は未入力**。第9期の公表値からの逆算。見える化には後期高齢者加入割合補正係数（令和9年度0.9558）が入っている</t>
+          <t>**見える化は未入力**。（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数で求めた値。後期高齢者加入割合補正係数（令和9年度0.9558ほか）は見える化に入っており、**所得段階別加入割合補正係数を入れれば見える化が自動で計算する**</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr"/>
       <c r="C20" s="7" t="n">
-        <v>5912</v>
+        <v>5810</v>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr">
@@ -6301,11 +6301,11 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>6379</v>
+        <v>6269</v>
       </c>
       <c r="C21" s="7" t="inlineStr"/>
       <c r="D21" s="7" t="n">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -7091,12 +7091,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>見込交付割合6.148％（第9期公表値からの逆算。基数は標準給付費見込額のみ）</t>
+          <t>見込交付割合5.533％（算式。基数は標準給付費見込額のみ）</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>後期高齢者加入割合補正係数はワークシートに入っている。所得段階別加入割合補正係数は未入力</t>
+          <t>後期高齢者加入割合補正係数はワークシートに入っている。**所得段階別加入割合補正係数（99行）を入れれば自動で計算される**</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260925.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>見える化の第10期3年計3,101,295千円に対し、こちらの算定は2,869,936千円。差は1.9％</t>
+          <t>見える化の第10期3年計3,101,295千円に対し、こちらの算定は2,869,936千円。差は+8.06%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>採用（相互に検証できた）</t>
+          <t>採用（令和8年度の置き方の違いとして説明できる）</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>不採用（自前の241,112千円を使う）</t>
+          <t>不採用（自前の224,013千円を使う）</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>3年計で+0.4％程度</t>
+          <t>3年計で+231,359千円（+8.06%）。いずれも総給付費どうしの比較</t>
         </is>
       </c>
     </row>
@@ -3067,6 +3067,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr"/>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -4366,6 +4367,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -4376,7 +4378,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>※ **回数の出所は見える化の方が正しい。**自前は国保連月報の実日数を回数に読み替えていたため、訪問介護で2割強、訪問看護で1割強、回数を少なく見ていた。</t>
+          <t>※ 回数の出所は見える化の方が正しい。自前は国保連月報の実日数を回数に読み替えていたため、訪問介護で2割強、訪問看護で1割強、回数を少なく見ていた。</t>
         </is>
       </c>
     </row>
@@ -5854,6 +5856,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -5940,7 +5943,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>見える化の方が1.9％高い</t>
+          <t>見える化の方が+8.06%</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5964,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>**見える化は未入力**。総給付費の4.7％（令和5〜7年度実績）</t>
+          <t>見える化は未入力。総給付費の4.7％（令和5〜7年度実績）</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5985,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>**見える化は未入力**。同2.3％</t>
+          <t>見える化は未入力。同2.3％</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6006,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>**見える化は未入力**。同0.25％</t>
+          <t>見える化は未入力。同0.25％</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6027,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>**見える化は未入力**。件数×60円の仮置き。見える化の参考係数では単価の上限が95円とされている</t>
+          <t>見える化は未入力。件数×60円の仮置き。見える化の参考係数では単価の上限が95円とされている</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6048,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>見える化は総給付費だけ。その他給付費を入れると自前と1.9％差になる</t>
+          <t>見える化の値は総給付費であり、その他給付費を含まない。自前の標準給付費と並べると+0.24%だが、これは見える化の総給付費と自前の標準給付費を比べた数字にすぎない。見える化にその他給付費224,013千円を足すと3,325,308千円となり、自前との差は+7.48%に広がる</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6069,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>**見える化は3シートとも全部ゼロ**。年報 様式4 の令和6年度決算を置いた</t>
+          <t>見える化は3シートとも全部ゼロ。年報 様式4 の令和6年度決算を置いた</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6174,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>**見える化は未入力**。年報 様式1 所得段階別（令和7年度末）の構成比による</t>
+          <t>見える化は未入力。年報 様式1 所得段階別（令和7年度末）の構成比による</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6195,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>**見える化は未入力**。（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数で求めた値。後期高齢者加入割合補正係数（令和9年度0.9558ほか）は見える化に入っており、**所得段階別加入割合補正係数を入れれば見える化が自動で計算する**</t>
+          <t>見える化は未入力。（第1号負担割合＋5％）－第1号負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数で求めた値。後期高齢者加入割合補正係数（令和9年度0.9558ほか）は見える化に入っており、所得段階別加入割合補正係数を入れれば見える化が自動で計算する</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6216,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>**見える化は未入力**。年報 様式4 の保有額は12,000千円</t>
+          <t>見える化は未入力。年報 様式4 の保有額は12,000千円</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6237,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>**見える化は未入力**。年報 様式3 の現年度分99.35％</t>
+          <t>見える化は未入力。年報 様式3 の現年度分99.35％</t>
         </is>
       </c>
     </row>
@@ -6301,11 +6304,11 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>6269</v>
+        <v>130</v>
       </c>
       <c r="C21" s="7" t="inlineStr"/>
       <c r="D21" s="7" t="n">
-        <v>459</v>
+        <v>-5680</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -6454,7 +6457,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>**令和6年度に993千円から5,305千円へ5.3倍。通いの場の展開が始まったとみられる。町に内訳を確認する**</t>
+          <t>令和6年度に993千円から5,305千円へ5.3倍。通いの場の展開が始まったとみられる。町に内訳を確認する</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6629,7 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>**令和3年度末0円→令和4年度末120,000千円→令和5年度末12,000千円。繰入金は全年度ゼロなのに残高が10分の1になっており内部矛盾がある。基金運用状況調書での確認を要する**</t>
+          <t>令和3年度末0円→令和4年度末120,000千円→令和5年度末12,000千円。繰入金は全年度ゼロなのに残高が10分の1になっており内部矛盾がある。基金運用状況調書での確認を要する</t>
         </is>
       </c>
     </row>
@@ -6700,10 +6703,11 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>※ 単位：円。年報 様式4「５．介護保険特別会計経理状況（1）保険事業勘定」の歳出の決算額。**令和7年度は年報そのものが未入力のため全科目ゼロ。**</t>
+          <t>※ 単位：円。年報 様式4「５．介護保険特別会計経理状況（1）保険事業勘定」の歳出の決算額。令和7年度は年報そのものが未入力のため全科目ゼロ。</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6980,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>国保連への支払実績。**町の決算で確認を要する**</t>
+          <t>国保連への支払実績。町の決算で確認を要する</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -7006,7 +7010,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>**残高の系列に内部矛盾があるため基金運用状況調書で要確認**</t>
+          <t>残高の系列に内部矛盾があるため基金運用状況調書で要確認</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
@@ -7096,7 +7100,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>後期高齢者加入割合補正係数はワークシートに入っている。**所得段階別加入割合補正係数（99行）を入れれば自動で計算される**</t>
+          <t>後期高齢者加入割合補正係数はワークシートに入っている。所得段階別加入割合補正係数（99行）を入れれば自動で計算される</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
@@ -7126,7 +7130,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>**04シート参照。通所リハは月報で横ばいなのに見える化は2.65倍**</t>
+          <t>04シート参照。通所リハは月報で横ばいなのに見える化は2.65倍</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_見える化ワークシートとの突合_20260925.xlsx
@@ -856,17 +856,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>年報 様式4 の保有額が令和4年度末120,000千円→令和5年度末12,000千円。繰入金は全年度ゼロで、内部矛盾がある</t>
+          <t>年報 様式4 の保有額（令和4年度末120,000千円・令和5年度末12,000千円）が、町の財務書類（令和4年度末90,000千円・令和5年度末120,000千円）と合わない</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>年報 様式4（令和4〜6年度）</t>
+          <t>年報 様式4（令和4〜6年度）／町の財務書類 附属明細書</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>要確認（基金運用状況調書）</t>
+          <t>財務書類を採用（令和7年度末は要確認）</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>見える化は未入力。年報 様式4 の保有額は12,000千円</t>
+          <t>見える化は未入力。残高は令和5年度末120,000千円（町の財務書類）、令和8年度末見込210,000千円</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       <c r="G9" s="7" t="n"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>令和3年度末0円→令和4年度末120,000千円→令和5年度末12,000千円。繰入金は全年度ゼロなのに残高が10分の1になっており内部矛盾がある。基金運用状況調書での確認を要する</t>
+          <t>年報の値は令和3年度末0円→令和4年度末120,000千円→令和5年度末12,000千円。町の財務書類（附属明細書「基金の明細」）では令和4年度末90,000千円・令和5年度末120,000千円で、年報の値は合わない。保険料の算定は財務書類の残高による</t>
         </is>
       </c>
     </row>
@@ -7005,12 +7005,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>残高12,000千円（年報 様式4）。取崩額は町の方針次第</t>
+          <t>残高は令和5年度末120,000千円（町の財務書類）、令和8年度末見込210,000千円。取崩額は町の方針次第</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>残高の系列に内部矛盾があるため基金運用状況調書で要確認</t>
+          <t>令和7年度末の残高（財産に関する調書）と令和8年度9月補正の積立の執行を確認</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
